--- a/docentes/Garcia Felix Jose Antonio - Estadisticos 20231.xlsx
+++ b/docentes/Garcia Felix Jose Antonio - Estadisticos 20231.xlsx
@@ -533,7 +533,7 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -542,13 +542,13 @@
         <v>3</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>91.18000000000001</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -559,7 +559,7 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -568,13 +568,13 @@
         <v>3</v>
       </c>
       <c r="F4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4">
-        <v>92.31</v>
+        <v>92.5</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -611,7 +611,7 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -620,10 +620,10 @@
         <v>12</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G6">
-        <v>69.23</v>
+        <v>68.42</v>
       </c>
       <c r="H6">
         <v>6.3</v>
@@ -777,13 +777,13 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -800,13 +800,13 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -846,13 +846,13 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E6">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1003,7 +1003,7 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1012,13 +1012,13 @@
         <v>3</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>91.18000000000001</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="H3">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1029,7 +1029,7 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1038,13 +1038,13 @@
         <v>3</v>
       </c>
       <c r="F4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4">
-        <v>92.31</v>
+        <v>92.5</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1081,7 +1081,7 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1090,10 +1090,10 @@
         <v>12</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G6">
-        <v>69.23</v>
+        <v>68.42</v>
       </c>
       <c r="H6">
         <v>6.3</v>

--- a/docentes/Garcia Felix Jose Antonio - Estadisticos 20231.xlsx
+++ b/docentes/Garcia Felix Jose Antonio - Estadisticos 20231.xlsx
@@ -94,22 +94,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
     <t>RUIZ</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>JORGE MARIO</t>
+    <t>NUBE</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ALEMAN</t>
+  </si>
+  <si>
+    <t>VANESA</t>
+  </si>
+  <si>
+    <t>CHRISTIAN YAIR</t>
   </si>
 </sst>
 </file>
@@ -533,7 +533,7 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -542,13 +542,13 @@
         <v>3</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>91.43000000000001</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -611,7 +611,7 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -620,10 +620,10 @@
         <v>12</v>
       </c>
       <c r="F6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>68.42</v>
+        <v>69.23</v>
       </c>
       <c r="H6">
         <v>6.3</v>
@@ -757,16 +757,19 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>74.06999999999999</v>
+      </c>
+      <c r="H2">
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -777,19 +780,22 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>94.12</v>
+      </c>
+      <c r="H3">
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -803,16 +809,19 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>95</v>
+      </c>
+      <c r="H4">
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -826,16 +835,19 @@
         <v>39</v>
       </c>
       <c r="D5">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>97.44</v>
+      </c>
+      <c r="H5">
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -846,19 +858,22 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>87.18000000000001</v>
+      </c>
+      <c r="H6">
+        <v>6.3</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -872,16 +887,19 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>96.88</v>
+      </c>
+      <c r="H7">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -895,16 +913,19 @@
         <v>30</v>
       </c>
       <c r="D8">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>96.67</v>
+      </c>
+      <c r="H8">
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -918,16 +939,19 @@
         <v>28</v>
       </c>
       <c r="D9">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>89.29000000000001</v>
+      </c>
+      <c r="H9">
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -983,16 +1007,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>81.48</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1003,22 +1027,22 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3">
         <v>32</v>
       </c>
       <c r="G3">
-        <v>91.43000000000001</v>
+        <v>94.12</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1035,16 +1059,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1061,16 +1085,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G5">
-        <v>94.87</v>
+        <v>97.44</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1081,22 +1105,22 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G6">
-        <v>68.42</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="H6">
-        <v>6.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1113,16 +1137,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G7">
-        <v>100</v>
+        <v>96.88</v>
       </c>
       <c r="H7">
-        <v>8.300000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1139,16 +1163,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G8">
-        <v>90</v>
+        <v>96.67</v>
       </c>
       <c r="H8">
-        <v>9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1165,13 +1189,13 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G9">
-        <v>96.43000000000001</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="H9">
         <v>8.5</v>
@@ -1216,7 +1240,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920153</v>
+        <v>23330051920327</v>
       </c>
       <c r="B2" t="s">
         <v>25</v>
@@ -1228,10 +1252,10 @@
         <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1239,7 +1263,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920209</v>
+        <v>20330051920100</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -1257,7 +1281,7 @@
         <v>18</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Garcia Felix Jose Antonio - Estadisticos 20231.xlsx
+++ b/docentes/Garcia Felix Jose Antonio - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -94,19 +94,10 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
     <t>NUBE</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>ALEMAN</t>
-  </si>
-  <si>
-    <t>VANESA</t>
   </si>
   <si>
     <t>CHRISTIAN YAIR</t>
@@ -1208,7 +1199,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1240,48 +1231,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920327</v>
+        <v>20330051920100</v>
       </c>
       <c r="B2" t="s">
         <v>25</v>
       </c>
       <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
         <v>27</v>
       </c>
-      <c r="D2" t="s">
-        <v>29</v>
-      </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G2">
         <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920100</v>
-      </c>
-      <c r="B3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Garcia Felix Jose Antonio - Estadisticos 20231.xlsx
+++ b/docentes/Garcia Felix Jose Antonio - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="31">
   <si>
     <t>Mat</t>
   </si>
@@ -97,10 +97,19 @@
     <t>NUBE</t>
   </si>
   <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
     <t>ALEMAN</t>
   </si>
   <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
     <t>CHRISTIAN YAIR</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
   </si>
 </sst>
 </file>
@@ -998,13 +1007,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>74.06999999999999</v>
+        <v>81.48</v>
       </c>
       <c r="H2">
         <v>7.4</v>
@@ -1024,16 +1033,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>94.12</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H3">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1050,13 +1059,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G4">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="H4">
         <v>8.800000000000001</v>
@@ -1076,16 +1085,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G5">
-        <v>97.44</v>
+        <v>94.87</v>
       </c>
       <c r="H5">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1102,16 +1111,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G6">
-        <v>87.18000000000001</v>
+        <v>84.62</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1137,7 +1146,7 @@
         <v>96.88</v>
       </c>
       <c r="H7">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1154,16 +1163,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G8">
-        <v>96.67</v>
+        <v>100</v>
       </c>
       <c r="H8">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1189,7 +1198,7 @@
         <v>89.29000000000001</v>
       </c>
       <c r="H9">
-        <v>8.5</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1199,7 +1208,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1237,10 +1246,10 @@
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -1250,6 +1259,29 @@
       </c>
       <c r="G2">
         <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920213</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Garcia Felix Jose Antonio - Estadisticos 20231.xlsx
+++ b/docentes/Garcia Felix Jose Antonio - Estadisticos 20231.xlsx
@@ -1016,7 +1016,7 @@
         <v>81.48</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1042,7 +1042,7 @@
         <v>91.18000000000001</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1068,7 +1068,7 @@
         <v>97.5</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1094,7 +1094,7 @@
         <v>94.87</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1120,7 +1120,7 @@
         <v>84.62</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1146,7 +1146,7 @@
         <v>96.88</v>
       </c>
       <c r="H7">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1172,7 +1172,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1198,7 +1198,7 @@
         <v>89.29000000000001</v>
       </c>
       <c r="H9">
-        <v>8</v>
+        <v>9.5</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Garcia Felix Jose Antonio - Estadisticos 20231.xlsx
+++ b/docentes/Garcia Felix Jose Antonio - Estadisticos 20231.xlsx
@@ -1016,7 +1016,7 @@
         <v>81.48</v>
       </c>
       <c r="H2">
-        <v>9.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1042,7 +1042,7 @@
         <v>91.18000000000001</v>
       </c>
       <c r="H3">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1068,7 +1068,7 @@
         <v>97.5</v>
       </c>
       <c r="H4">
-        <v>9.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1094,7 +1094,7 @@
         <v>94.87</v>
       </c>
       <c r="H5">
-        <v>9.699999999999999</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1120,7 +1120,7 @@
         <v>84.62</v>
       </c>
       <c r="H6">
-        <v>9.199999999999999</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1146,7 +1146,7 @@
         <v>96.88</v>
       </c>
       <c r="H7">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1172,7 +1172,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1198,7 +1198,7 @@
         <v>89.29000000000001</v>
       </c>
       <c r="H9">
-        <v>9.5</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1258,7 +1258,7 @@
         <v>18</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
